--- a/03_Outputs/Bioenergetica_Norte/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/08_Educacion/educacion.xlsx
@@ -6098,13 +6098,13 @@
         <v>2021</v>
       </c>
       <c r="F175" s="7">
-        <v>0.781615020785788</v>
+        <v>0.796964299121351</v>
       </c>
       <c r="G175" s="9">
-        <v>0.0112764137586522</v>
+        <v>0.0485385898098528</v>
       </c>
       <c r="H175" s="11">
-        <v>0.0850725122576275</v>
+        <v>0.0593047332771143</v>
       </c>
     </row>
     <row r="176">
@@ -6132,13 +6132,13 @@
         <v>2021</v>
       </c>
       <c r="F176" s="7">
-        <v>0.7845193732626</v>
+        <v>0.875338763762797</v>
       </c>
       <c r="G176" s="9">
-        <v>0.0118559014701181</v>
+        <v>0.054261116476724</v>
       </c>
       <c r="H176" s="11">
-        <v>0.0850952404724102</v>
+        <v>0.0674233977206876</v>
       </c>
     </row>
     <row r="177">
@@ -6166,13 +6166,13 @@
         <v>2021</v>
       </c>
       <c r="F177" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G177" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H177" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="178">
